--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.7231520616442</v>
+        <v>11.65501221001718</v>
       </c>
       <c r="D2" t="n">
-        <v>15.03329637837291</v>
+        <v>2.442910661485598</v>
       </c>
       <c r="E2" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F2" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.14311561463094</v>
+        <v>8.960756287377528</v>
       </c>
       <c r="D3" t="n">
-        <v>17.69564360143863</v>
+        <v>2.875542085233777</v>
       </c>
       <c r="E3" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F3" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.52490668663661</v>
+        <v>9.347797336578449</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43074902771996</v>
+        <v>3.807496717004494</v>
       </c>
       <c r="E4" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F4" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.2872865908994</v>
+        <v>9.959184071021152</v>
       </c>
       <c r="D5" t="n">
-        <v>32.99904581831162</v>
+        <v>5.362344945475638</v>
       </c>
       <c r="E5" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F5" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.8613793134169</v>
+        <v>7.452474138430247</v>
       </c>
       <c r="D6" t="n">
-        <v>32.65348373451139</v>
+        <v>5.306191106858101</v>
       </c>
       <c r="E6" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F6" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.94851157076266</v>
+        <v>4.866633130248933</v>
       </c>
       <c r="D7" t="n">
-        <v>29.56769190580744</v>
+        <v>4.804749934693708</v>
       </c>
       <c r="E7" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F7" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.888606396726</v>
+        <v>6.969398539467976</v>
       </c>
       <c r="D8" t="n">
-        <v>42.02876842453806</v>
+        <v>6.829674868987435</v>
       </c>
       <c r="E8" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F8" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27145252689905</v>
+        <v>5.569111035621097</v>
       </c>
       <c r="D9" t="n">
-        <v>33.84987806363561</v>
+        <v>5.500605185340787</v>
       </c>
       <c r="E9" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F9" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.15896395116958</v>
+        <v>3.438331642065057</v>
       </c>
       <c r="D10" t="n">
-        <v>21.58139323040975</v>
+        <v>3.506976399941584</v>
       </c>
       <c r="E10" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F10" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.13706012255152</v>
+        <v>8.309772269914621</v>
       </c>
       <c r="D11" t="n">
-        <v>51.56284578419613</v>
+        <v>8.378962439931872</v>
       </c>
       <c r="E11" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F11" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.7893135611566</v>
+        <v>9.553263453687947</v>
       </c>
       <c r="D12" t="n">
-        <v>59.12681711331687</v>
+        <v>9.608107780913992</v>
       </c>
       <c r="E12" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F12" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>6.198221814457966</v>
+        <v>1.00721104484942</v>
       </c>
       <c r="D13" t="n">
-        <v>6.011670449578606</v>
+        <v>0.9768964480565235</v>
       </c>
       <c r="E13" t="n">
-        <v>17.99631959608326</v>
+        <v>2.924401934363531</v>
       </c>
       <c r="F13" t="n">
-        <v>14.58129882303333</v>
+        <v>2.369461058742917</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
